--- a/Datas/FishData.xlsx
+++ b/Datas/FishData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="110">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -342,18 +342,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>List&lt;int&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>places</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SmallFish</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>虹鳟鱼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -476,6 +464,21 @@
   <si>
     <t>水母</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fish</t>
+  </si>
+  <si>
+    <t>鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -858,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F46"/>
+  <dimension ref="A2:E46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="10.375" customWidth="1"/>
@@ -866,7 +869,7 @@
     <col min="5" max="5" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -882,11 +885,8 @@
       <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -902,11 +902,8 @@
       <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1000</v>
       </c>
@@ -916,8 +913,14 @@
       <c r="C4" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1001</v>
       </c>
@@ -928,10 +931,13 @@
         <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="E5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1002</v>
       </c>
@@ -941,8 +947,14 @@
       <c r="C6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1003</v>
       </c>
@@ -953,10 +965,13 @@
         <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="E7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1004</v>
       </c>
@@ -966,8 +981,14 @@
       <c r="C8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1005</v>
       </c>
@@ -977,8 +998,14 @@
       <c r="C9" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1006</v>
       </c>
@@ -988,8 +1015,14 @@
       <c r="C10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1007</v>
       </c>
@@ -999,8 +1032,14 @@
       <c r="C11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1008</v>
       </c>
@@ -1010,8 +1049,14 @@
       <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1009</v>
       </c>
@@ -1021,8 +1066,14 @@
       <c r="C13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1010</v>
       </c>
@@ -1032,8 +1083,14 @@
       <c r="C14" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1011</v>
       </c>
@@ -1043,8 +1100,14 @@
       <c r="C15" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1012</v>
       </c>
@@ -1054,8 +1117,14 @@
       <c r="C16" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1013</v>
       </c>
@@ -1065,8 +1134,14 @@
       <c r="C17" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1014</v>
       </c>
@@ -1076,8 +1151,14 @@
       <c r="C18" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1015</v>
       </c>
@@ -1087,8 +1168,14 @@
       <c r="C19" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1016</v>
       </c>
@@ -1098,8 +1185,14 @@
       <c r="C20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1017</v>
       </c>
@@ -1109,8 +1202,14 @@
       <c r="C21" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1018</v>
       </c>
@@ -1121,10 +1220,13 @@
         <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="E22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1019</v>
       </c>
@@ -1134,8 +1236,14 @@
       <c r="C23" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1020</v>
       </c>
@@ -1145,8 +1253,14 @@
       <c r="C24" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D24" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1021</v>
       </c>
@@ -1156,8 +1270,14 @@
       <c r="C25" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D25" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1022</v>
       </c>
@@ -1167,8 +1287,14 @@
       <c r="C26" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1023</v>
       </c>
@@ -1178,8 +1304,14 @@
       <c r="C27" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1024</v>
       </c>
@@ -1189,8 +1321,14 @@
       <c r="C28" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D28" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1100</v>
       </c>
@@ -1201,10 +1339,13 @@
         <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="E29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1101</v>
       </c>
@@ -1214,8 +1355,14 @@
       <c r="C30" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1102</v>
       </c>
@@ -1226,10 +1373,13 @@
         <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="E31" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1103</v>
       </c>
@@ -1239,8 +1389,14 @@
       <c r="C32" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1104</v>
       </c>
@@ -1251,10 +1407,13 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="E33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1105</v>
       </c>
@@ -1264,8 +1423,14 @@
       <c r="C34" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1106</v>
       </c>
@@ -1275,8 +1440,14 @@
       <c r="C35" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1107</v>
       </c>
@@ -1286,8 +1457,14 @@
       <c r="C36" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D36" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1108</v>
       </c>
@@ -1297,8 +1474,14 @@
       <c r="C37" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D37" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1109</v>
       </c>
@@ -1308,8 +1491,14 @@
       <c r="C38" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D38" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1110</v>
       </c>
@@ -1319,8 +1508,14 @@
       <c r="C39" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1111</v>
       </c>
@@ -1330,8 +1525,14 @@
       <c r="C40" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D40" t="s">
+        <v>106</v>
+      </c>
+      <c r="E40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1112</v>
       </c>
@@ -1341,8 +1542,14 @@
       <c r="C41" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E41" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1113</v>
       </c>
@@ -1352,8 +1559,14 @@
       <c r="C42" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D42" t="s">
+        <v>106</v>
+      </c>
+      <c r="E42" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1114</v>
       </c>
@@ -1363,8 +1576,14 @@
       <c r="C43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D43" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1115</v>
       </c>
@@ -1374,8 +1593,14 @@
       <c r="C44" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D44" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1116</v>
       </c>
@@ -1385,8 +1610,14 @@
       <c r="C45" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D45" t="s">
+        <v>106</v>
+      </c>
+      <c r="E45" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1117</v>
       </c>
@@ -1395,23 +1626,30 @@
       </c>
       <c r="C46" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="D46" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:O31"/>
+  <dimension ref="B4:O74"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:15" s="6" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1435,7 +1673,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>22</v>
@@ -1444,7 +1682,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
@@ -1475,7 +1713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1488,7 +1726,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="2:15" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1507,7 +1745,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -1520,13 +1758,13 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="N8" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -1545,25 +1783,25 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="2:15" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>39</v>
@@ -1572,10 +1810,10 @@
         <v>60</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>36</v>
@@ -1584,9 +1822,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -1605,7 +1843,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
@@ -1626,7 +1864,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1645,46 +1883,46 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="2:15" s="6" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O14" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1703,7 +1941,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -1722,7 +1960,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1741,9 +1979,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="2:15" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
@@ -1759,16 +1997,16 @@
         <v>52</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>64</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>54</v>
@@ -1780,7 +2018,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1799,7 +2037,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1818,7 +2056,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1837,7 +2075,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="2:15" s="6" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -1856,37 +2094,37 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="2:15" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>36</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>50</v>
@@ -1895,7 +2133,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -1914,7 +2152,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="2:15" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="N25" s="2" t="s">
         <v>51</v>
       </c>
@@ -1922,15 +2160,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="2:15" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="N26" s="2" t="s">
         <v>52</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N27" s="3" t="s">
         <v>64</v>
       </c>
@@ -1938,7 +2176,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="F28" s="6" t="s">
+        <v>108</v>
+      </c>
       <c r="N28" s="3" t="s">
         <v>57</v>
       </c>
@@ -1946,7 +2187,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N29" s="3" t="s">
         <v>54</v>
       </c>
@@ -1954,17 +2195,232 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N30" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O30" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N31" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+      <c r="C32" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C40" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C42" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C46" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C47" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C48" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C51" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C52" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C53" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C55" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C56" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C57" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C58" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C59" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C60" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C61" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C62" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C63" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C64" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C65" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C66" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C67" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C68" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C69" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C70" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C71" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C72" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C73" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C74" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:U50"/>
+  <dimension ref="B2:U103"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="3:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -2268,7 +2724,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
       <c r="F17" s="3" t="s">
         <v>17</v>
       </c>
@@ -2280,7 +2736,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
       <c r="F18" s="3" t="s">
         <v>18</v>
       </c>
@@ -2292,7 +2748,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="6:21" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" ht="15" x14ac:dyDescent="0.2">
       <c r="F19" s="3" t="s">
         <v>19</v>
       </c>
@@ -2331,7 +2787,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="6:21" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" ht="28.5" x14ac:dyDescent="0.2">
       <c r="F20" s="3" t="s">
         <v>20</v>
       </c>
@@ -2370,7 +2826,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="6:21" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:21" ht="15" x14ac:dyDescent="0.2">
       <c r="F21" s="3" t="s">
         <v>21</v>
       </c>
@@ -2409,7 +2865,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="6:21" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:21" ht="15" x14ac:dyDescent="0.2">
       <c r="F22" s="3" t="s">
         <v>22</v>
       </c>
@@ -2448,7 +2904,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
       <c r="F23" s="3" t="s">
         <v>31</v>
       </c>
@@ -2460,19 +2916,19 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
       <c r="I24" s="3"/>
       <c r="K24" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
       <c r="I25" s="3"/>
       <c r="K25" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="6:21" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:21" ht="15" x14ac:dyDescent="0.2">
       <c r="I26" s="3"/>
       <c r="K26" s="3" t="s">
         <v>44</v>
@@ -2481,7 +2937,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
       <c r="I27" s="3"/>
       <c r="K27" s="3" t="s">
         <v>43</v>
@@ -2490,7 +2946,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
       <c r="I28" s="3"/>
       <c r="K28" s="3" t="s">
         <v>41</v>
@@ -2499,16 +2955,34 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="6:21" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:21" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="I29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="I30" s="3"/>
       <c r="K30" s="3" t="s">
         <v>50</v>
@@ -2517,7 +2991,16 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="I31" s="3"/>
       <c r="K31" s="3" t="s">
         <v>58</v>
@@ -2526,7 +3009,16 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="6:21" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" ht="15" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I32" s="3"/>
       <c r="K32" s="2" t="s">
         <v>51</v>
@@ -2535,7 +3027,16 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="9:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="I33" s="3"/>
       <c r="K33" s="2" t="s">
         <v>52</v>
@@ -2544,7 +3045,16 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="I34" s="3"/>
       <c r="K34" s="3" t="s">
         <v>64</v>
@@ -2553,7 +3063,16 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="I35" s="3"/>
       <c r="K35" s="3" t="s">
         <v>57</v>
@@ -2562,7 +3081,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="I36" s="3"/>
       <c r="K36" s="3" t="s">
         <v>54</v>
@@ -2571,7 +3099,16 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="I37" s="3"/>
       <c r="K37" s="3" t="s">
         <v>68</v>
@@ -2580,7 +3117,10 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>45</v>
+      </c>
       <c r="I38" s="3"/>
       <c r="K38" s="3" t="s">
         <v>70</v>
@@ -2589,73 +3129,914 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B39" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="I39" s="3"/>
       <c r="M39" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="I40" s="3"/>
       <c r="M40" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="9:13" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="I41" s="3"/>
       <c r="M41" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="I42" s="3"/>
       <c r="M42" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="I43" s="3"/>
       <c r="M43" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="9:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>65</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="M44" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="9:13" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>41</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="M45" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>47</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="M46" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="M47" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="9:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="M48" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B49" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="M49" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
       <c r="M50" s="3" t="s">
         <v>70</v>
       </c>
     </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="J60" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" t="s">
+        <v>1</v>
+      </c>
+      <c r="L60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="15" x14ac:dyDescent="0.2">
+      <c r="E61" t="s">
+        <v>63</v>
+      </c>
+      <c r="F61">
+        <f>VLOOKUP(E61,$J$60:$K$103,2,FALSE)</f>
+        <v>1005</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K61">
+        <v>1000</v>
+      </c>
+      <c r="L61" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E62" t="s">
+        <v>50</v>
+      </c>
+      <c r="F62">
+        <f t="shared" ref="F62:F96" si="0">VLOOKUP(E62,$J$60:$K$103,2,FALSE)</f>
+        <v>1007</v>
+      </c>
+      <c r="J62" t="s">
+        <v>51</v>
+      </c>
+      <c r="K62">
+        <v>1001</v>
+      </c>
+      <c r="L62" s="5">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E63" t="s">
+        <v>45</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="0"/>
+        <v>1009</v>
+      </c>
+      <c r="J63" t="s">
+        <v>33</v>
+      </c>
+      <c r="K63">
+        <v>1002</v>
+      </c>
+      <c r="L63" s="5">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E64" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="0"/>
+        <v>1011</v>
+      </c>
+      <c r="J64" t="s">
+        <v>36</v>
+      </c>
+      <c r="K64">
+        <v>1003</v>
+      </c>
+      <c r="L64" s="5">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="65" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E65" t="s">
+        <v>43</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="0"/>
+        <v>1014</v>
+      </c>
+      <c r="J65" t="s">
+        <v>33</v>
+      </c>
+      <c r="K65">
+        <v>1004</v>
+      </c>
+      <c r="L65" s="5">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="66" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E66" t="s">
+        <v>41</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="0"/>
+        <v>1016</v>
+      </c>
+      <c r="J66" t="s">
+        <v>63</v>
+      </c>
+      <c r="K66">
+        <v>1005</v>
+      </c>
+      <c r="L66" s="5">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="67" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E67" t="s">
+        <v>47</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="0"/>
+        <v>1017</v>
+      </c>
+      <c r="J67" t="s">
+        <v>64</v>
+      </c>
+      <c r="K67">
+        <v>1006</v>
+      </c>
+      <c r="L67" s="5">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="68" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E68" t="s">
+        <v>58</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="0"/>
+        <v>1022</v>
+      </c>
+      <c r="J68" t="s">
+        <v>50</v>
+      </c>
+      <c r="K68">
+        <v>1007</v>
+      </c>
+      <c r="L68" s="5">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="69" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E69" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="0"/>
+        <v>1024</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K69">
+        <v>1008</v>
+      </c>
+      <c r="L69" s="5">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="70" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E70" t="s">
+        <v>52</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J70" t="s">
+        <v>45</v>
+      </c>
+      <c r="K70">
+        <v>1009</v>
+      </c>
+      <c r="L70" s="5">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="71" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E71" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="0"/>
+        <v>1002</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K71">
+        <v>1010</v>
+      </c>
+      <c r="L71" s="5">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="72" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E72" t="s">
+        <v>36</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="J72" t="s">
+        <v>44</v>
+      </c>
+      <c r="K72">
+        <v>1011</v>
+      </c>
+      <c r="L72" s="5">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="73" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E73" t="s">
+        <v>35</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="0"/>
+        <v>1008</v>
+      </c>
+      <c r="J73" t="s">
+        <v>57</v>
+      </c>
+      <c r="K73">
+        <v>1012</v>
+      </c>
+      <c r="L73" s="5">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="74" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E74" t="s">
+        <v>39</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="J74" t="s">
+        <v>38</v>
+      </c>
+      <c r="K74">
+        <v>1013</v>
+      </c>
+      <c r="L74" s="5">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="75" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E75" t="s">
+        <v>38</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="0"/>
+        <v>1013</v>
+      </c>
+      <c r="J75" t="s">
+        <v>43</v>
+      </c>
+      <c r="K75">
+        <v>1014</v>
+      </c>
+      <c r="L75" s="5">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="76" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E76" t="s">
+        <v>59</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="0"/>
+        <v>1018</v>
+      </c>
+      <c r="J76" t="s">
+        <v>65</v>
+      </c>
+      <c r="K76">
+        <v>1015</v>
+      </c>
+      <c r="L76" s="5">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="77" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E77" t="s">
+        <v>60</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="J77" t="s">
+        <v>41</v>
+      </c>
+      <c r="K77">
+        <v>1016</v>
+      </c>
+      <c r="L77" s="5">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="78" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E78" t="s">
+        <v>40</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="0"/>
+        <v>1023</v>
+      </c>
+      <c r="J78" t="s">
+        <v>47</v>
+      </c>
+      <c r="K78">
+        <v>1017</v>
+      </c>
+      <c r="L78" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="79" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E79" t="s">
+        <v>52</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J79" t="s">
+        <v>59</v>
+      </c>
+      <c r="K79">
+        <v>1018</v>
+      </c>
+      <c r="L79" s="5">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="80" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E80" t="s">
+        <v>51</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="0"/>
+        <v>1001</v>
+      </c>
+      <c r="J80" t="s">
+        <v>54</v>
+      </c>
+      <c r="K80">
+        <v>1019</v>
+      </c>
+      <c r="L80" s="5">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="81" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E81" t="s">
+        <v>33</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="0"/>
+        <v>1002</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K81">
+        <v>1020</v>
+      </c>
+      <c r="L81" s="5">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="82" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E82" t="s">
+        <v>36</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="J82" t="s">
+        <v>56</v>
+      </c>
+      <c r="K82">
+        <v>1021</v>
+      </c>
+      <c r="L82" s="5">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="83" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E83" t="s">
+        <v>64</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="J83" t="s">
+        <v>58</v>
+      </c>
+      <c r="K83">
+        <v>1022</v>
+      </c>
+      <c r="L83" s="5">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="84" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E84" t="s">
+        <v>50</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="0"/>
+        <v>1007</v>
+      </c>
+      <c r="J84" t="s">
+        <v>40</v>
+      </c>
+      <c r="K84">
+        <v>1023</v>
+      </c>
+      <c r="L84" s="5">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="85" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E85" t="s">
+        <v>57</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="0"/>
+        <v>1012</v>
+      </c>
+      <c r="J85" t="s">
+        <v>42</v>
+      </c>
+      <c r="K85">
+        <v>1024</v>
+      </c>
+      <c r="L85" s="5">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="86" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E86" t="s">
+        <v>54</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="0"/>
+        <v>1019</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K86">
+        <v>1100</v>
+      </c>
+      <c r="L86" s="5">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="87" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E87" t="s">
+        <v>60</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K87">
+        <v>1101</v>
+      </c>
+      <c r="L87" s="5">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="88" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E88" t="s">
+        <v>52</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K88">
+        <v>1102</v>
+      </c>
+      <c r="L88" s="5">
+        <v>4102</v>
+      </c>
+    </row>
+    <row r="89" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E89" t="s">
+        <v>51</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="0"/>
+        <v>1001</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K89">
+        <v>1103</v>
+      </c>
+      <c r="L89" s="5">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="90" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E90" t="s">
+        <v>36</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K90">
+        <v>1104</v>
+      </c>
+      <c r="L90" s="5">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="91" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E91" t="s">
+        <v>64</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K91">
+        <v>1105</v>
+      </c>
+      <c r="L91" s="5">
+        <v>4105</v>
+      </c>
+    </row>
+    <row r="92" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E92" t="s">
+        <v>50</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="0"/>
+        <v>1007</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K92">
+        <v>1106</v>
+      </c>
+      <c r="L92" s="5">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="93" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E93" t="s">
+        <v>57</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="0"/>
+        <v>1012</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K93">
+        <v>1107</v>
+      </c>
+      <c r="L93" s="5">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="94" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E94" t="s">
+        <v>65</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="0"/>
+        <v>1015</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K94">
+        <v>1108</v>
+      </c>
+      <c r="L94" s="5">
+        <v>4108</v>
+      </c>
+    </row>
+    <row r="95" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E95" t="s">
+        <v>54</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="0"/>
+        <v>1019</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K95">
+        <v>1109</v>
+      </c>
+      <c r="L95" s="5">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="96" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E96" t="s">
+        <v>56</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="0"/>
+        <v>1021</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K96">
+        <v>1110</v>
+      </c>
+      <c r="L96" s="5">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="97" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J97" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K97">
+        <v>1111</v>
+      </c>
+      <c r="L97" s="5">
+        <v>4111</v>
+      </c>
+    </row>
+    <row r="98" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J98" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K98">
+        <v>1112</v>
+      </c>
+      <c r="L98" s="5">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="99" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J99" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K99">
+        <v>1113</v>
+      </c>
+      <c r="L99" s="5">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="100" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100">
+        <v>1114</v>
+      </c>
+      <c r="L100" s="5">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="101" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J101" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K101">
+        <v>1115</v>
+      </c>
+      <c r="L101" s="5">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="102" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K102">
+        <v>1116</v>
+      </c>
+      <c r="L102" s="5">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="103" spans="10:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J103" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K103">
+        <v>1117</v>
+      </c>
+      <c r="L103" s="5">
+        <v>4117</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Datas/FishData.xlsx
+++ b/Datas/FishData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="116">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -479,6 +479,30 @@
   <si>
     <t>洞穴天使鱼</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>places</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seasons</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -861,15 +885,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E46"/>
+  <dimension ref="A2:I46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="15.375" customWidth="1"/>
-    <col min="5" max="5" width="13.75" customWidth="1"/>
+    <col min="3" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -880,13 +904,25 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -897,13 +933,25 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="G3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1000</v>
       </c>
@@ -913,14 +961,17 @@
       <c r="C4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
         <v>106</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1001</v>
       </c>
@@ -931,13 +982,16 @@
         <v>51</v>
       </c>
       <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
         <v>106</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1002</v>
       </c>
@@ -948,13 +1002,16 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
         <v>106</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1003</v>
       </c>
@@ -965,13 +1022,16 @@
         <v>36</v>
       </c>
       <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
         <v>106</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1004</v>
       </c>
@@ -982,13 +1042,16 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
         <v>106</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1005</v>
       </c>
@@ -999,13 +1062,16 @@
         <v>63</v>
       </c>
       <c r="D9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" t="s">
         <v>106</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1006</v>
       </c>
@@ -1016,13 +1082,16 @@
         <v>64</v>
       </c>
       <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
         <v>106</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1007</v>
       </c>
@@ -1033,13 +1102,16 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
         <v>106</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1008</v>
       </c>
@@ -1049,14 +1121,17 @@
       <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
         <v>106</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1009</v>
       </c>
@@ -1067,13 +1142,16 @@
         <v>45</v>
       </c>
       <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
         <v>106</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1010</v>
       </c>
@@ -1083,14 +1161,17 @@
       <c r="C14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" t="s">
         <v>106</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1011</v>
       </c>
@@ -1101,13 +1182,16 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
         <v>106</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1012</v>
       </c>
@@ -1118,13 +1202,16 @@
         <v>57</v>
       </c>
       <c r="D16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" t="s">
         <v>106</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1013</v>
       </c>
@@ -1135,13 +1222,16 @@
         <v>38</v>
       </c>
       <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" t="s">
         <v>106</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1014</v>
       </c>
@@ -1152,13 +1242,16 @@
         <v>43</v>
       </c>
       <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
         <v>106</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1015</v>
       </c>
@@ -1169,13 +1262,16 @@
         <v>65</v>
       </c>
       <c r="D19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" t="s">
         <v>106</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1016</v>
       </c>
@@ -1186,13 +1282,16 @@
         <v>41</v>
       </c>
       <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
         <v>106</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1017</v>
       </c>
@@ -1203,13 +1302,16 @@
         <v>47</v>
       </c>
       <c r="D21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" t="s">
         <v>106</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1018</v>
       </c>
@@ -1220,13 +1322,16 @@
         <v>59</v>
       </c>
       <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" t="s">
         <v>106</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1019</v>
       </c>
@@ -1237,13 +1342,16 @@
         <v>54</v>
       </c>
       <c r="D23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" t="s">
         <v>106</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1020</v>
       </c>
@@ -1253,14 +1361,17 @@
       <c r="C24" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" t="s">
         <v>106</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1021</v>
       </c>
@@ -1271,13 +1382,16 @@
         <v>56</v>
       </c>
       <c r="D25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" t="s">
         <v>106</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1022</v>
       </c>
@@ -1288,13 +1402,16 @@
         <v>58</v>
       </c>
       <c r="D26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" t="s">
         <v>106</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1023</v>
       </c>
@@ -1305,13 +1422,16 @@
         <v>40</v>
       </c>
       <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" t="s">
         <v>106</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1024</v>
       </c>
@@ -1322,13 +1442,16 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" t="s">
         <v>106</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1100</v>
       </c>
@@ -1338,14 +1461,17 @@
       <c r="C29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
         <v>106</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1101</v>
       </c>
@@ -1355,14 +1481,17 @@
       <c r="C30" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
         <v>106</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1102</v>
       </c>
@@ -1372,14 +1501,17 @@
       <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" t="s">
         <v>106</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1103</v>
       </c>
@@ -1389,14 +1521,17 @@
       <c r="C32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
         <v>106</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1104</v>
       </c>
@@ -1406,14 +1541,17 @@
       <c r="C33" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
         <v>106</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1105</v>
       </c>
@@ -1423,14 +1561,17 @@
       <c r="C34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" t="s">
         <v>106</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1106</v>
       </c>
@@ -1440,14 +1581,17 @@
       <c r="C35" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
         <v>106</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1107</v>
       </c>
@@ -1457,14 +1601,17 @@
       <c r="C36" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" t="s">
         <v>106</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1108</v>
       </c>
@@ -1474,14 +1621,17 @@
       <c r="C37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
         <v>106</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1109</v>
       </c>
@@ -1491,14 +1641,17 @@
       <c r="C38" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" t="s">
         <v>106</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1110</v>
       </c>
@@ -1508,14 +1661,17 @@
       <c r="C39" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" t="s">
         <v>106</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1111</v>
       </c>
@@ -1525,14 +1681,17 @@
       <c r="C40" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" t="s">
         <v>106</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1112</v>
       </c>
@@ -1542,14 +1701,17 @@
       <c r="C41" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
         <v>106</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1113</v>
       </c>
@@ -1559,14 +1721,17 @@
       <c r="C42" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" t="s">
         <v>106</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1114</v>
       </c>
@@ -1576,14 +1741,17 @@
       <c r="C43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" t="s">
         <v>106</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1115</v>
       </c>
@@ -1593,14 +1761,17 @@
       <c r="C44" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" t="s">
         <v>106</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1116</v>
       </c>
@@ -1610,14 +1781,17 @@
       <c r="C45" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s">
         <v>106</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1117</v>
       </c>
@@ -1627,10 +1801,13 @@
       <c r="C46" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" t="s">
         <v>106</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>107</v>
       </c>
     </row>

--- a/Datas/FishData.xlsx
+++ b/Datas/FishData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="126">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -503,6 +503,37 @@
   <si>
     <t>seasons</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2355</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>水母</t>
+  </si>
+  <si>
+    <t>鱿鱼</t>
+  </si>
+  <si>
+    <t>695,512,889</t>
+  </si>
+  <si>
+    <t>302,759,695,512,889</t>
+  </si>
+  <si>
+    <t>759,695,512,889</t>
+  </si>
+  <si>
+    <t>302,759</t>
+  </si>
+  <si>
+    <t>302,759,2355</t>
   </si>
 </sst>
 </file>
@@ -891,6 +922,7 @@
     <col min="3" max="4" width="10.375" customWidth="1"/>
     <col min="5" max="5" width="15.375" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -970,6 +1002,12 @@
       <c r="F4" t="s">
         <v>107</v>
       </c>
+      <c r="H4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -990,6 +1028,12 @@
       <c r="F5" t="s">
         <v>107</v>
       </c>
+      <c r="H5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I5" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -1010,6 +1054,12 @@
       <c r="F6" t="s">
         <v>107</v>
       </c>
+      <c r="H6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -1030,6 +1080,12 @@
       <c r="F7" t="s">
         <v>107</v>
       </c>
+      <c r="H7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I7" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -1050,6 +1106,12 @@
       <c r="F8" t="s">
         <v>107</v>
       </c>
+      <c r="H8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I8" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -1070,6 +1132,12 @@
       <c r="F9" t="s">
         <v>107</v>
       </c>
+      <c r="H9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I9" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -1090,6 +1158,12 @@
       <c r="F10" t="s">
         <v>107</v>
       </c>
+      <c r="H10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I10" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -1110,6 +1184,12 @@
       <c r="F11" t="s">
         <v>107</v>
       </c>
+      <c r="H11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I11" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -1130,6 +1210,12 @@
       <c r="F12" t="s">
         <v>107</v>
       </c>
+      <c r="H12" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -1150,6 +1236,12 @@
       <c r="F13" t="s">
         <v>107</v>
       </c>
+      <c r="H13" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
@@ -1170,6 +1262,12 @@
       <c r="F14" t="s">
         <v>107</v>
       </c>
+      <c r="H14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -1190,6 +1288,12 @@
       <c r="F15" t="s">
         <v>107</v>
       </c>
+      <c r="H15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I15" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -1210,8 +1314,14 @@
       <c r="F16" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>124</v>
+      </c>
+      <c r="I16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1013</v>
       </c>
@@ -1230,8 +1340,14 @@
       <c r="F17" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1014</v>
       </c>
@@ -1250,8 +1366,14 @@
       <c r="F18" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>117</v>
+      </c>
+      <c r="I18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1015</v>
       </c>
@@ -1270,8 +1392,14 @@
       <c r="F19" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1016</v>
       </c>
@@ -1290,8 +1418,14 @@
       <c r="F20" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>117</v>
+      </c>
+      <c r="I20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1017</v>
       </c>
@@ -1310,8 +1444,14 @@
       <c r="F21" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>117</v>
+      </c>
+      <c r="I21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1018</v>
       </c>
@@ -1330,8 +1470,14 @@
       <c r="F22" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>121</v>
+      </c>
+      <c r="I22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1019</v>
       </c>
@@ -1350,8 +1496,14 @@
       <c r="F23" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1020</v>
       </c>
@@ -1370,8 +1522,14 @@
       <c r="F24" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>123</v>
+      </c>
+      <c r="I24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1021</v>
       </c>
@@ -1390,8 +1548,14 @@
       <c r="F25" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1022</v>
       </c>
@@ -1410,8 +1574,14 @@
       <c r="F26" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>117</v>
+      </c>
+      <c r="I26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1023</v>
       </c>
@@ -1430,8 +1600,14 @@
       <c r="F27" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>121</v>
+      </c>
+      <c r="I27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1024</v>
       </c>
@@ -1450,8 +1626,14 @@
       <c r="F28" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1100</v>
       </c>
@@ -1470,8 +1652,14 @@
       <c r="F29" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H29">
+        <v>2497</v>
+      </c>
+      <c r="I29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1101</v>
       </c>
@@ -1490,8 +1678,14 @@
       <c r="F30" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H30">
+        <v>2497</v>
+      </c>
+      <c r="I30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1102</v>
       </c>
@@ -1510,8 +1704,14 @@
       <c r="F31" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H31">
+        <v>2497</v>
+      </c>
+      <c r="I31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1103</v>
       </c>
@@ -1530,8 +1730,14 @@
       <c r="F32" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H32">
+        <v>2497</v>
+      </c>
+      <c r="I32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1104</v>
       </c>
@@ -1550,8 +1756,14 @@
       <c r="F33" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H33">
+        <v>2497</v>
+      </c>
+      <c r="I33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1105</v>
       </c>
@@ -1570,8 +1782,14 @@
       <c r="F34" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H34">
+        <v>2497</v>
+      </c>
+      <c r="I34" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1106</v>
       </c>
@@ -1590,8 +1808,14 @@
       <c r="F35" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H35">
+        <v>2497</v>
+      </c>
+      <c r="I35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1107</v>
       </c>
@@ -1610,8 +1834,14 @@
       <c r="F36" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H36">
+        <v>2497</v>
+      </c>
+      <c r="I36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1108</v>
       </c>
@@ -1630,8 +1860,14 @@
       <c r="F37" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H37">
+        <v>2497</v>
+      </c>
+      <c r="I37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1109</v>
       </c>
@@ -1650,8 +1886,14 @@
       <c r="F38" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H38">
+        <v>2497</v>
+      </c>
+      <c r="I38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1110</v>
       </c>
@@ -1670,8 +1912,14 @@
       <c r="F39" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H39">
+        <v>2497</v>
+      </c>
+      <c r="I39" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1111</v>
       </c>
@@ -1690,8 +1938,14 @@
       <c r="F40" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H40">
+        <v>2497</v>
+      </c>
+      <c r="I40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1112</v>
       </c>
@@ -1710,8 +1964,14 @@
       <c r="F41" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H41">
+        <v>2497</v>
+      </c>
+      <c r="I41" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1113</v>
       </c>
@@ -1730,8 +1990,14 @@
       <c r="F42" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H42">
+        <v>2497</v>
+      </c>
+      <c r="I42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1114</v>
       </c>
@@ -1750,8 +2016,14 @@
       <c r="F43" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H43">
+        <v>2497</v>
+      </c>
+      <c r="I43" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1115</v>
       </c>
@@ -1770,8 +2042,14 @@
       <c r="F44" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H44">
+        <v>2497</v>
+      </c>
+      <c r="I44" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1116</v>
       </c>
@@ -1790,8 +2068,14 @@
       <c r="F45" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H45">
+        <v>2497</v>
+      </c>
+      <c r="I45" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1117</v>
       </c>
@@ -1809,6 +2093,12 @@
       </c>
       <c r="F46" t="s">
         <v>107</v>
+      </c>
+      <c r="H46">
+        <v>2497</v>
+      </c>
+      <c r="I46" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2660,7 +2950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:U103"/>
+  <dimension ref="B2:U153"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="3:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -4135,7 +4425,7 @@
         <v>4110</v>
       </c>
     </row>
-    <row r="97" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="5:12" x14ac:dyDescent="0.2">
       <c r="J97" s="3" t="s">
         <v>17</v>
       </c>
@@ -4146,7 +4436,7 @@
         <v>4111</v>
       </c>
     </row>
-    <row r="98" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="98" spans="5:12" x14ac:dyDescent="0.2">
       <c r="J98" s="3" t="s">
         <v>32</v>
       </c>
@@ -4157,7 +4447,7 @@
         <v>4112</v>
       </c>
     </row>
-    <row r="99" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="99" spans="5:12" x14ac:dyDescent="0.2">
       <c r="J99" s="3" t="s">
         <v>30</v>
       </c>
@@ -4168,7 +4458,7 @@
         <v>4113</v>
       </c>
     </row>
-    <row r="100" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="100" spans="5:12" x14ac:dyDescent="0.2">
       <c r="J100" s="3" t="s">
         <v>16</v>
       </c>
@@ -4179,7 +4469,7 @@
         <v>4114</v>
       </c>
     </row>
-    <row r="101" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="5:12" x14ac:dyDescent="0.2">
       <c r="J101" s="3" t="s">
         <v>29</v>
       </c>
@@ -4190,7 +4480,7 @@
         <v>4115</v>
       </c>
     </row>
-    <row r="102" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="5:12" x14ac:dyDescent="0.2">
       <c r="J102" s="3" t="s">
         <v>14</v>
       </c>
@@ -4201,7 +4491,7 @@
         <v>4116</v>
       </c>
     </row>
-    <row r="103" spans="10:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="5:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="J103" s="3" t="s">
         <v>20</v>
       </c>
@@ -4210,6 +4500,342 @@
       </c>
       <c r="L103" s="5">
         <v>4117</v>
+      </c>
+    </row>
+    <row r="112" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E112" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="113" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E113" t="s">
+        <v>20</v>
+      </c>
+      <c r="F113">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="114" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E114" t="s">
+        <v>26</v>
+      </c>
+      <c r="F114">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="115" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E115" t="s">
+        <v>41</v>
+      </c>
+      <c r="F115" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="116" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E116" t="s">
+        <v>45</v>
+      </c>
+      <c r="F116" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="117" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E117" t="s">
+        <v>42</v>
+      </c>
+      <c r="F117" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E118" t="s">
+        <v>56</v>
+      </c>
+      <c r="F118" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E119" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="120" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E120" t="s">
+        <v>31</v>
+      </c>
+      <c r="F120">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="121" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F121">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="122" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E122" t="s">
+        <v>32</v>
+      </c>
+      <c r="F122">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="123" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E123" t="s">
+        <v>65</v>
+      </c>
+      <c r="F123" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="124" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E124" t="s">
+        <v>52</v>
+      </c>
+      <c r="F124" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E125" t="s">
+        <v>14</v>
+      </c>
+      <c r="F125">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="126" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E126" t="s">
+        <v>47</v>
+      </c>
+      <c r="F126" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="127" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E127" t="s">
+        <v>39</v>
+      </c>
+      <c r="F127" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="128" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E128" t="s">
+        <v>58</v>
+      </c>
+      <c r="F128" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="129" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E129" t="s">
+        <v>38</v>
+      </c>
+      <c r="F129" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="130" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E130" t="s">
+        <v>30</v>
+      </c>
+      <c r="F130">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="131" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E131" t="s">
+        <v>33</v>
+      </c>
+      <c r="F131" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="132" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E132" t="s">
+        <v>64</v>
+      </c>
+      <c r="F132" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="133" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E133" t="s">
+        <v>29</v>
+      </c>
+      <c r="F133">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="134" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E134" t="s">
+        <v>54</v>
+      </c>
+      <c r="F134" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="135" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E135" t="s">
+        <v>27</v>
+      </c>
+      <c r="F135">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="136" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E136" t="s">
+        <v>51</v>
+      </c>
+      <c r="F136" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="137" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E137" t="s">
+        <v>59</v>
+      </c>
+      <c r="F137" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="138" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E138" t="s">
+        <v>35</v>
+      </c>
+      <c r="F138" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="139" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E139" t="s">
+        <v>16</v>
+      </c>
+      <c r="F139">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="140" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E140" t="s">
+        <v>24</v>
+      </c>
+      <c r="F140">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="141" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E141" t="s">
+        <v>18</v>
+      </c>
+      <c r="F141">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="142" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E142" t="s">
+        <v>50</v>
+      </c>
+      <c r="F142" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="143" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E143" t="s">
+        <v>119</v>
+      </c>
+      <c r="F143">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="144" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E144" t="s">
+        <v>57</v>
+      </c>
+      <c r="F144" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="145" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E145" t="s">
+        <v>60</v>
+      </c>
+      <c r="F145" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="146" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E146" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="147" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E147" t="s">
+        <v>63</v>
+      </c>
+      <c r="F147" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="148" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E148" t="s">
+        <v>44</v>
+      </c>
+      <c r="F148" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="149" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E149" t="s">
+        <v>36</v>
+      </c>
+      <c r="F149" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="150" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E150" t="s">
+        <v>40</v>
+      </c>
+      <c r="F150" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="151" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E151" t="s">
+        <v>43</v>
+      </c>
+      <c r="F151" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="152" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E152" t="s">
+        <v>120</v>
+      </c>
+      <c r="F152">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="153" spans="5:6" x14ac:dyDescent="0.2">
+      <c r="E153" t="s">
+        <v>25</v>
+      </c>
+      <c r="F153">
+        <v>2497</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/FishData.xlsx
+++ b/Datas/FishData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="134">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -534,6 +534,38 @@
   </si>
   <si>
     <t>302,759,2355</t>
+  </si>
+  <si>
+    <t>章鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锦鲤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2355,889</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2355,889</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>695,512,889,302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红鲷鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -583,7 +615,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,6 +625,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -609,7 +647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -636,6 +674,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -916,13 +964,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I46"/>
+  <dimension ref="A2:I34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="4" width="10.375" customWidth="1"/>
     <col min="5" max="5" width="15.375" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
-    <col min="8" max="8" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="17.5" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -947,7 +995,7 @@
       <c r="G2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="13" t="s">
         <v>112</v>
       </c>
       <c r="I2" t="s">
@@ -976,7 +1024,7 @@
       <c r="G3" t="s">
         <v>110</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="13" t="s">
         <v>113</v>
       </c>
       <c r="I3" t="s">
@@ -1002,7 +1050,7 @@
       <c r="F4" t="s">
         <v>107</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="13" t="s">
         <v>122</v>
       </c>
       <c r="I4" t="s">
@@ -1011,16 +1059,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="B5" s="5">
-        <v>4001</v>
+        <v>4006</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
         <v>106</v>
@@ -1028,7 +1076,7 @@
       <c r="F5" t="s">
         <v>107</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="13" t="s">
         <v>124</v>
       </c>
       <c r="I5" t="s">
@@ -1037,16 +1085,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="B6" s="5">
-        <v>4002</v>
+        <v>4007</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>106</v>
@@ -1054,8 +1102,8 @@
       <c r="F6" t="s">
         <v>107</v>
       </c>
-      <c r="H6" t="s">
-        <v>123</v>
+      <c r="H6" s="13" t="s">
+        <v>125</v>
       </c>
       <c r="I6" t="s">
         <v>116</v>
@@ -1063,16 +1111,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="B7" s="5">
-        <v>4003</v>
+        <v>4009</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>106</v>
@@ -1080,8 +1128,8 @@
       <c r="F7" t="s">
         <v>107</v>
       </c>
-      <c r="H7" t="s">
-        <v>122</v>
+      <c r="H7" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="I7" t="s">
         <v>116</v>
@@ -1089,16 +1137,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="B8" s="5">
-        <v>4004</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
+        <v>4010</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>106</v>
@@ -1106,25 +1154,25 @@
       <c r="F8" t="s">
         <v>107</v>
       </c>
-      <c r="H8" t="s">
-        <v>123</v>
+      <c r="H8" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="I8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="B9" s="5">
-        <v>4005</v>
+        <v>4011</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>106</v>
@@ -1132,7 +1180,7 @@
       <c r="F9" t="s">
         <v>107</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="13" t="s">
         <v>117</v>
       </c>
       <c r="I9" t="s">
@@ -1141,16 +1189,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="B10" s="5">
-        <v>4006</v>
+        <v>4013</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
         <v>106</v>
@@ -1158,8 +1206,8 @@
       <c r="F10" t="s">
         <v>107</v>
       </c>
-      <c r="H10" t="s">
-        <v>124</v>
+      <c r="H10" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="I10" t="s">
         <v>116</v>
@@ -1167,16 +1215,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="B11" s="5">
-        <v>4007</v>
+        <v>4014</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
         <v>106</v>
@@ -1184,8 +1232,8 @@
       <c r="F11" t="s">
         <v>107</v>
       </c>
-      <c r="H11" t="s">
-        <v>125</v>
+      <c r="H11" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="I11" t="s">
         <v>116</v>
@@ -1193,16 +1241,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="B12" s="5">
-        <v>4008</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>35</v>
+        <v>4015</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
       </c>
       <c r="E12" t="s">
         <v>106</v>
@@ -1210,8 +1258,8 @@
       <c r="F12" t="s">
         <v>107</v>
       </c>
-      <c r="H12" t="s">
-        <v>121</v>
+      <c r="H12" s="13" t="s">
+        <v>118</v>
       </c>
       <c r="I12" t="s">
         <v>116</v>
@@ -1219,16 +1267,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="B13" s="5">
-        <v>4009</v>
+        <v>4016</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
         <v>106</v>
@@ -1236,7 +1284,7 @@
       <c r="F13" t="s">
         <v>107</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="13" t="s">
         <v>117</v>
       </c>
       <c r="I13" t="s">
@@ -1245,16 +1293,16 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="B14" s="5">
-        <v>4010</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>39</v>
+        <v>4017</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
       </c>
       <c r="E14" t="s">
         <v>106</v>
@@ -1262,8 +1310,8 @@
       <c r="F14" t="s">
         <v>107</v>
       </c>
-      <c r="H14" t="s">
-        <v>121</v>
+      <c r="H14" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="I14" t="s">
         <v>116</v>
@@ -1271,16 +1319,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="B15" s="5">
-        <v>4011</v>
+        <v>4018</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
         <v>106</v>
@@ -1288,8 +1336,8 @@
       <c r="F15" t="s">
         <v>107</v>
       </c>
-      <c r="H15" t="s">
-        <v>117</v>
+      <c r="H15" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="I15" t="s">
         <v>116</v>
@@ -1297,16 +1345,16 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="B16" s="5">
-        <v>4012</v>
-      </c>
-      <c r="C16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" t="s">
-        <v>57</v>
+        <v>4020</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="E16" t="s">
         <v>106</v>
@@ -1314,8 +1362,8 @@
       <c r="F16" t="s">
         <v>107</v>
       </c>
-      <c r="H16" t="s">
-        <v>124</v>
+      <c r="H16" s="13" t="s">
+        <v>123</v>
       </c>
       <c r="I16" t="s">
         <v>116</v>
@@ -1323,16 +1371,16 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="B17" s="5">
-        <v>4013</v>
+        <v>4021</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
         <v>106</v>
@@ -1340,8 +1388,8 @@
       <c r="F17" t="s">
         <v>107</v>
       </c>
-      <c r="H17" t="s">
-        <v>121</v>
+      <c r="H17" s="13" t="s">
+        <v>118</v>
       </c>
       <c r="I17" t="s">
         <v>116</v>
@@ -1349,16 +1397,16 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="B18" s="5">
-        <v>4014</v>
+        <v>4022</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
         <v>106</v>
@@ -1366,7 +1414,7 @@
       <c r="F18" t="s">
         <v>107</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="13" t="s">
         <v>117</v>
       </c>
       <c r="I18" t="s">
@@ -1375,16 +1423,16 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="B19" s="5">
-        <v>4015</v>
+        <v>4023</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
         <v>106</v>
@@ -1392,8 +1440,8 @@
       <c r="F19" t="s">
         <v>107</v>
       </c>
-      <c r="H19" t="s">
-        <v>118</v>
+      <c r="H19" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="I19" t="s">
         <v>116</v>
@@ -1401,16 +1449,16 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="B20" s="5">
-        <v>4016</v>
+        <v>4024</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
         <v>106</v>
@@ -1418,7 +1466,7 @@
       <c r="F20" t="s">
         <v>107</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="13" t="s">
         <v>117</v>
       </c>
       <c r="I20" t="s">
@@ -1427,16 +1475,16 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>1017</v>
+        <v>1100</v>
       </c>
       <c r="B21" s="5">
-        <v>4017</v>
-      </c>
-      <c r="C21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" t="s">
-        <v>47</v>
+        <v>4100</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E21" t="s">
         <v>106</v>
@@ -1444,8 +1492,8 @@
       <c r="F21" t="s">
         <v>107</v>
       </c>
-      <c r="H21" t="s">
-        <v>117</v>
+      <c r="H21" s="13">
+        <v>2497</v>
       </c>
       <c r="I21" t="s">
         <v>116</v>
@@ -1453,16 +1501,16 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>1018</v>
+        <v>1101</v>
       </c>
       <c r="B22" s="5">
-        <v>4018</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>59</v>
+        <v>4101</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="E22" t="s">
         <v>106</v>
@@ -1470,8 +1518,8 @@
       <c r="F22" t="s">
         <v>107</v>
       </c>
-      <c r="H22" t="s">
-        <v>121</v>
+      <c r="H22" s="13">
+        <v>2497</v>
       </c>
       <c r="I22" t="s">
         <v>116</v>
@@ -1479,16 +1527,16 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>1019</v>
+        <v>1103</v>
       </c>
       <c r="B23" s="5">
-        <v>4019</v>
-      </c>
-      <c r="C23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" t="s">
-        <v>54</v>
+        <v>4103</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E23" t="s">
         <v>106</v>
@@ -1496,8 +1544,8 @@
       <c r="F23" t="s">
         <v>107</v>
       </c>
-      <c r="H23" t="s">
-        <v>124</v>
+      <c r="H23" s="13">
+        <v>2497</v>
       </c>
       <c r="I23" t="s">
         <v>116</v>
@@ -1505,16 +1553,16 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>1020</v>
+        <v>1105</v>
       </c>
       <c r="B24" s="5">
-        <v>4020</v>
+        <v>4105</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s">
         <v>106</v>
@@ -1522,8 +1570,8 @@
       <c r="F24" t="s">
         <v>107</v>
       </c>
-      <c r="H24" t="s">
-        <v>123</v>
+      <c r="H24" s="13">
+        <v>2497</v>
       </c>
       <c r="I24" t="s">
         <v>116</v>
@@ -1531,16 +1579,16 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>1021</v>
+        <v>1106</v>
       </c>
       <c r="B25" s="5">
-        <v>4021</v>
-      </c>
-      <c r="C25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" t="s">
-        <v>56</v>
+        <v>4106</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E25" t="s">
         <v>106</v>
@@ -1548,8 +1596,8 @@
       <c r="F25" t="s">
         <v>107</v>
       </c>
-      <c r="H25" t="s">
-        <v>118</v>
+      <c r="H25" s="13">
+        <v>2497</v>
       </c>
       <c r="I25" t="s">
         <v>116</v>
@@ -1557,16 +1605,16 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>1022</v>
+        <v>1109</v>
       </c>
       <c r="B26" s="5">
-        <v>4022</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" t="s">
-        <v>58</v>
+        <v>4109</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="E26" t="s">
         <v>106</v>
@@ -1574,8 +1622,8 @@
       <c r="F26" t="s">
         <v>107</v>
       </c>
-      <c r="H26" t="s">
-        <v>117</v>
+      <c r="H26" s="13">
+        <v>2497</v>
       </c>
       <c r="I26" t="s">
         <v>116</v>
@@ -1583,16 +1631,16 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>1023</v>
+        <v>1110</v>
       </c>
       <c r="B27" s="5">
-        <v>4023</v>
-      </c>
-      <c r="C27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" t="s">
-        <v>40</v>
+        <v>4110</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="E27" t="s">
         <v>106</v>
@@ -1600,8 +1648,8 @@
       <c r="F27" t="s">
         <v>107</v>
       </c>
-      <c r="H27" t="s">
-        <v>121</v>
+      <c r="H27" s="13">
+        <v>2497</v>
       </c>
       <c r="I27" t="s">
         <v>116</v>
@@ -1609,16 +1657,16 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>1024</v>
+        <v>1111</v>
       </c>
       <c r="B28" s="5">
-        <v>4024</v>
-      </c>
-      <c r="C28" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" t="s">
-        <v>42</v>
+        <v>4111</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="E28" t="s">
         <v>106</v>
@@ -1626,8 +1674,8 @@
       <c r="F28" t="s">
         <v>107</v>
       </c>
-      <c r="H28" t="s">
-        <v>117</v>
+      <c r="H28" s="13">
+        <v>2497</v>
       </c>
       <c r="I28" t="s">
         <v>116</v>
@@ -1635,16 +1683,16 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>1100</v>
+        <v>1112</v>
       </c>
       <c r="B29" s="5">
-        <v>4100</v>
+        <v>4112</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
         <v>106</v>
@@ -1652,7 +1700,7 @@
       <c r="F29" t="s">
         <v>107</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="13">
         <v>2497</v>
       </c>
       <c r="I29" t="s">
@@ -1661,16 +1709,16 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="B30" s="5">
-        <v>4101</v>
+        <v>4113</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
         <v>106</v>
@@ -1678,7 +1726,7 @@
       <c r="F30" t="s">
         <v>107</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="13">
         <v>2497</v>
       </c>
       <c r="I30" t="s">
@@ -1687,16 +1735,16 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>1102</v>
+        <v>1114</v>
       </c>
       <c r="B31" s="5">
-        <v>4102</v>
+        <v>4114</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
         <v>106</v>
@@ -1704,7 +1752,7 @@
       <c r="F31" t="s">
         <v>107</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="13">
         <v>2497</v>
       </c>
       <c r="I31" t="s">
@@ -1713,16 +1761,16 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="B32" s="5">
-        <v>4103</v>
+        <v>4115</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
         <v>106</v>
@@ -1730,7 +1778,7 @@
       <c r="F32" t="s">
         <v>107</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="13">
         <v>2497</v>
       </c>
       <c r="I32" t="s">
@@ -1739,16 +1787,16 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>1104</v>
+        <v>1116</v>
       </c>
       <c r="B33" s="5">
-        <v>4104</v>
+        <v>4116</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E33" t="s">
         <v>106</v>
@@ -1756,7 +1804,7 @@
       <c r="F33" t="s">
         <v>107</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="13">
         <v>2497</v>
       </c>
       <c r="I33" t="s">
@@ -1765,16 +1813,16 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>1105</v>
+        <v>1117</v>
       </c>
       <c r="B34" s="5">
-        <v>4105</v>
+        <v>4117</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="E34" t="s">
         <v>106</v>
@@ -1782,322 +1830,10 @@
       <c r="F34" t="s">
         <v>107</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="13">
         <v>2497</v>
       </c>
       <c r="I34" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>1106</v>
-      </c>
-      <c r="B35" s="5">
-        <v>4106</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" t="s">
-        <v>107</v>
-      </c>
-      <c r="H35">
-        <v>2497</v>
-      </c>
-      <c r="I35" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>1107</v>
-      </c>
-      <c r="B36" s="5">
-        <v>4107</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E36" t="s">
-        <v>106</v>
-      </c>
-      <c r="F36" t="s">
-        <v>107</v>
-      </c>
-      <c r="H36">
-        <v>2497</v>
-      </c>
-      <c r="I36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>1108</v>
-      </c>
-      <c r="B37" s="5">
-        <v>4108</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" t="s">
-        <v>106</v>
-      </c>
-      <c r="F37" t="s">
-        <v>107</v>
-      </c>
-      <c r="H37">
-        <v>2497</v>
-      </c>
-      <c r="I37" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>1109</v>
-      </c>
-      <c r="B38" s="5">
-        <v>4109</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" t="s">
-        <v>106</v>
-      </c>
-      <c r="F38" t="s">
-        <v>107</v>
-      </c>
-      <c r="H38">
-        <v>2497</v>
-      </c>
-      <c r="I38" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>1110</v>
-      </c>
-      <c r="B39" s="5">
-        <v>4110</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" t="s">
-        <v>106</v>
-      </c>
-      <c r="F39" t="s">
-        <v>107</v>
-      </c>
-      <c r="H39">
-        <v>2497</v>
-      </c>
-      <c r="I39" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>1111</v>
-      </c>
-      <c r="B40" s="5">
-        <v>4111</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" t="s">
-        <v>106</v>
-      </c>
-      <c r="F40" t="s">
-        <v>107</v>
-      </c>
-      <c r="H40">
-        <v>2497</v>
-      </c>
-      <c r="I40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>1112</v>
-      </c>
-      <c r="B41" s="5">
-        <v>4112</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E41" t="s">
-        <v>106</v>
-      </c>
-      <c r="F41" t="s">
-        <v>107</v>
-      </c>
-      <c r="H41">
-        <v>2497</v>
-      </c>
-      <c r="I41" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>1113</v>
-      </c>
-      <c r="B42" s="5">
-        <v>4113</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E42" t="s">
-        <v>106</v>
-      </c>
-      <c r="F42" t="s">
-        <v>107</v>
-      </c>
-      <c r="H42">
-        <v>2497</v>
-      </c>
-      <c r="I42" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>1114</v>
-      </c>
-      <c r="B43" s="5">
-        <v>4114</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43" t="s">
-        <v>106</v>
-      </c>
-      <c r="F43" t="s">
-        <v>107</v>
-      </c>
-      <c r="H43">
-        <v>2497</v>
-      </c>
-      <c r="I43" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>1115</v>
-      </c>
-      <c r="B44" s="5">
-        <v>4115</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E44" t="s">
-        <v>106</v>
-      </c>
-      <c r="F44" t="s">
-        <v>107</v>
-      </c>
-      <c r="H44">
-        <v>2497</v>
-      </c>
-      <c r="I44" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>1116</v>
-      </c>
-      <c r="B45" s="5">
-        <v>4116</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" t="s">
-        <v>106</v>
-      </c>
-      <c r="F45" t="s">
-        <v>107</v>
-      </c>
-      <c r="H45">
-        <v>2497</v>
-      </c>
-      <c r="I45" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>1117</v>
-      </c>
-      <c r="B46" s="5">
-        <v>4117</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" t="s">
-        <v>106</v>
-      </c>
-      <c r="F46" t="s">
-        <v>107</v>
-      </c>
-      <c r="H46">
-        <v>2497</v>
-      </c>
-      <c r="I46" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2121,7 +1857,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="10" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -2133,7 +1869,7 @@
       <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -2142,7 +1878,7 @@
       <c r="J4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="10" t="s">
         <v>22</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -2161,7 +1897,7 @@
       <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="10" t="s">
         <v>27</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -2171,13 +1907,13 @@
         <v>29</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
@@ -2258,13 +1994,13 @@
       <c r="D10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="10" t="s">
         <v>87</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>103</v>
       </c>
       <c r="H10" s="3" t="s">
@@ -2355,7 +2091,7 @@
         <v>98</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="10" t="s">
         <v>97</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -2434,11 +2170,17 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
+      <c r="L17" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="N17" s="7" t="s">
         <v>45</v>
       </c>
@@ -2451,31 +2193,31 @@
         <v>88</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="10" t="s">
         <v>36</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="10" t="s">
         <v>87</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="10" t="s">
         <v>86</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="L18" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N18" s="3" t="s">
@@ -2548,7 +2290,9 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -2566,7 +2310,7 @@
         <v>84</v>
       </c>
       <c r="C23" s="3"/>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="12" t="s">
         <v>83</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -2575,16 +2319,16 @@
       <c r="F23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="10" t="s">
         <v>36</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="10" t="s">
         <v>79</v>
       </c>
       <c r="K23" s="3" t="s">

--- a/Datas/FishData.xlsx
+++ b/Datas/FishData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -243,6 +243,316 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>手套蟹.</t>
+  </si>
+  <si>
+    <t>泥鳅</t>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+  </si>
+  <si>
+    <t>蝾螈</t>
+  </si>
+  <si>
+    <t>罗非鱼</t>
+  </si>
+  <si>
+    <t>钻石鲟鱼</t>
+  </si>
+  <si>
+    <t>鲑鱼</t>
+  </si>
+  <si>
+    <t>梭鲈</t>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+  </si>
+  <si>
+    <t>黄鲈鱼</t>
+  </si>
+  <si>
+    <t>雀鳝鱼</t>
+  </si>
+  <si>
+    <t>溪鳟鱼</t>
+  </si>
+  <si>
+    <t>鲮鱼</t>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+  </si>
+  <si>
+    <t>鱿鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梭鲈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲑鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗非鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲑鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗非鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梭鲈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套蟹.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲮鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>泥鳅</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>城门河</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梭鲈</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>农场河</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲷鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>樱桃鲑鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>线鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丁鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>溪鳟鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>山地湖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广场河</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银龙鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兰寿金鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>小龙虾</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>住宅区河</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水母</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fish</t>
+  </si>
+  <si>
+    <t>鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>places</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seasons</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2355</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>水母</t>
+  </si>
+  <si>
+    <t>鱿鱼</t>
+  </si>
+  <si>
+    <t>695,512,889</t>
+  </si>
+  <si>
+    <t>302,759,695,512,889</t>
+  </si>
+  <si>
+    <t>759,695,512,889</t>
+  </si>
+  <si>
+    <t>302,759</t>
+  </si>
+  <si>
+    <t>302,759,2355</t>
+  </si>
+  <si>
+    <t>章鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锦鲤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2355,889</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2355,889</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>695,512,889,302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红鲷鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>River: </t>
     </r>
@@ -255,316 +565,6 @@
       </rPr>
       <t>Angelfish, Arapaima, Arowana, Barbel Steed, Betta, Bitterling, Black Bass, Bluegill, Brook Trout, Crucian Carp, Dace, Dorado, Freshwater Eel, Freshwater Goby, Giant Catfish, Guppy, Herabuna, Large Bass, Loach, Mitten Crab, Neon Tetra, Nibble Fish, Pale Chub, Pike, Piranha, Pond Smelt, Rainbow Trout, Saddled Bichir, Snapping Turtle, Soft-Shelled Turtle (Green), Soft-Shelled Turtle (Brown), Soft-Shelled Turtle (Black), Sweetfish</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手套蟹.</t>
-  </si>
-  <si>
-    <t>泥鳅</t>
-  </si>
-  <si>
-    <t>鲫鱼</t>
-  </si>
-  <si>
-    <t>蝾螈</t>
-  </si>
-  <si>
-    <t>罗非鱼</t>
-  </si>
-  <si>
-    <t>钻石鲟鱼</t>
-  </si>
-  <si>
-    <t>鲑鱼</t>
-  </si>
-  <si>
-    <t>梭鲈</t>
-  </si>
-  <si>
-    <t>孔雀鱼</t>
-  </si>
-  <si>
-    <t>霓虹脂鲤</t>
-  </si>
-  <si>
-    <t>桃花鱼</t>
-  </si>
-  <si>
-    <t>黄鲈鱼</t>
-  </si>
-  <si>
-    <t>雀鳝鱼</t>
-  </si>
-  <si>
-    <t>溪鳟鱼</t>
-  </si>
-  <si>
-    <t>鲮鱼</t>
-  </si>
-  <si>
-    <t>虹鳟鱼</t>
-  </si>
-  <si>
-    <t>鱿鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梭鲈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鲑鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗非鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虹鳟鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃花鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>霓虹脂鲤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃花鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水母</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虹鳟鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鲑鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃花鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虹鳟鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗非鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梭鲈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手套蟹.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>鲮鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>泥鳅</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>城门河</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃花鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梭鲈</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>农场河</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>霓虹脂鲤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>孔雀鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>洞穴天使鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>鲷鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>樱桃鲑鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>线鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>金鳟鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丁鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>溪鳟鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>山地湖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广场河</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>银龙鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>霓虹脂鲤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兰寿金鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>小龙虾</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>住宅区河</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水母</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fish</t>
-  </si>
-  <si>
-    <t>鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>洞穴天使鱼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>info</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;int&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>places</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seasons</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2355</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>水母</t>
-  </si>
-  <si>
-    <t>鱿鱼</t>
-  </si>
-  <si>
-    <t>695,512,889</t>
-  </si>
-  <si>
-    <t>302,759,695,512,889</t>
-  </si>
-  <si>
-    <t>759,695,512,889</t>
-  </si>
-  <si>
-    <t>302,759</t>
-  </si>
-  <si>
-    <t>302,759,2355</t>
-  </si>
-  <si>
-    <t>章鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金鳟鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>锦鲤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2355,889</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2355,889</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>695,512,889,302</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红鲷鱼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -984,7 +984,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -996,10 +996,10 @@
         <v>6</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -1013,7 +1013,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
@@ -1022,13 +1022,13 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.2">
@@ -1039,22 +1039,22 @@
         <v>4000</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" t="s">
         <v>106</v>
       </c>
-      <c r="F4" t="s">
-        <v>107</v>
-      </c>
       <c r="H4" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -1065,22 +1065,22 @@
         <v>4006</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" t="s">
         <v>106</v>
       </c>
-      <c r="F5" t="s">
-        <v>107</v>
-      </c>
       <c r="H5" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -1091,22 +1091,22 @@
         <v>4007</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" t="s">
         <v>106</v>
       </c>
-      <c r="F6" t="s">
-        <v>107</v>
-      </c>
       <c r="H6" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -1123,16 +1123,16 @@
         <v>45</v>
       </c>
       <c r="E7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" t="s">
         <v>106</v>
       </c>
-      <c r="F7" t="s">
-        <v>107</v>
-      </c>
       <c r="H7" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -1149,16 +1149,16 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s">
         <v>106</v>
       </c>
-      <c r="F8" t="s">
-        <v>107</v>
-      </c>
       <c r="H8" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1175,16 +1175,16 @@
         <v>44</v>
       </c>
       <c r="E9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" t="s">
         <v>106</v>
       </c>
-      <c r="F9" t="s">
-        <v>107</v>
-      </c>
       <c r="H9" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -1201,16 +1201,16 @@
         <v>38</v>
       </c>
       <c r="E10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" t="s">
         <v>106</v>
       </c>
-      <c r="F10" t="s">
-        <v>107</v>
-      </c>
       <c r="H10" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -1227,16 +1227,16 @@
         <v>43</v>
       </c>
       <c r="E11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" t="s">
         <v>106</v>
       </c>
-      <c r="F11" t="s">
-        <v>107</v>
-      </c>
       <c r="H11" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -1247,22 +1247,22 @@
         <v>4015</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" t="s">
         <v>106</v>
       </c>
-      <c r="F12" t="s">
-        <v>107</v>
-      </c>
       <c r="H12" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -1279,16 +1279,16 @@
         <v>41</v>
       </c>
       <c r="E13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" t="s">
         <v>106</v>
       </c>
-      <c r="F13" t="s">
-        <v>107</v>
-      </c>
       <c r="H13" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -1305,16 +1305,16 @@
         <v>47</v>
       </c>
       <c r="E14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" t="s">
         <v>106</v>
       </c>
-      <c r="F14" t="s">
-        <v>107</v>
-      </c>
       <c r="H14" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -1325,22 +1325,22 @@
         <v>4018</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" t="s">
         <v>106</v>
       </c>
-      <c r="F15" t="s">
-        <v>107</v>
-      </c>
       <c r="H15" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -1351,22 +1351,22 @@
         <v>4020</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" t="s">
         <v>106</v>
       </c>
-      <c r="F16" t="s">
-        <v>107</v>
-      </c>
       <c r="H16" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -1377,22 +1377,22 @@
         <v>4021</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" t="s">
         <v>106</v>
       </c>
-      <c r="F17" t="s">
-        <v>107</v>
-      </c>
       <c r="H17" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1403,22 +1403,22 @@
         <v>4022</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" t="s">
         <v>106</v>
       </c>
-      <c r="F18" t="s">
-        <v>107</v>
-      </c>
       <c r="H18" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1435,16 +1435,16 @@
         <v>40</v>
       </c>
       <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
         <v>106</v>
       </c>
-      <c r="F19" t="s">
-        <v>107</v>
-      </c>
       <c r="H19" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1461,16 +1461,16 @@
         <v>42</v>
       </c>
       <c r="E20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" t="s">
         <v>106</v>
       </c>
-      <c r="F20" t="s">
-        <v>107</v>
-      </c>
       <c r="H20" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -1487,16 +1487,16 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" t="s">
         <v>106</v>
-      </c>
-      <c r="F21" t="s">
-        <v>107</v>
       </c>
       <c r="H21" s="13">
         <v>2497</v>
       </c>
       <c r="I21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
@@ -1513,16 +1513,16 @@
         <v>25</v>
       </c>
       <c r="E22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" t="s">
         <v>106</v>
-      </c>
-      <c r="F22" t="s">
-        <v>107</v>
       </c>
       <c r="H22" s="13">
         <v>2497</v>
       </c>
       <c r="I22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -1539,16 +1539,16 @@
         <v>31</v>
       </c>
       <c r="E23" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" t="s">
         <v>106</v>
-      </c>
-      <c r="F23" t="s">
-        <v>107</v>
       </c>
       <c r="H23" s="13">
         <v>2497</v>
       </c>
       <c r="I23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
@@ -1559,22 +1559,22 @@
         <v>4105</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E24" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" t="s">
         <v>106</v>
-      </c>
-      <c r="F24" t="s">
-        <v>107</v>
       </c>
       <c r="H24" s="13">
         <v>2497</v>
       </c>
       <c r="I24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
@@ -1591,16 +1591,16 @@
         <v>26</v>
       </c>
       <c r="E25" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" t="s">
         <v>106</v>
-      </c>
-      <c r="F25" t="s">
-        <v>107</v>
       </c>
       <c r="H25" s="13">
         <v>2497</v>
       </c>
       <c r="I25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
@@ -1617,16 +1617,16 @@
         <v>28</v>
       </c>
       <c r="E26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" t="s">
         <v>106</v>
-      </c>
-      <c r="F26" t="s">
-        <v>107</v>
       </c>
       <c r="H26" s="13">
         <v>2497</v>
       </c>
       <c r="I26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
@@ -1637,22 +1637,22 @@
         <v>4110</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" t="s">
         <v>106</v>
-      </c>
-      <c r="F27" t="s">
-        <v>107</v>
       </c>
       <c r="H27" s="13">
         <v>2497</v>
       </c>
       <c r="I27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
@@ -1669,16 +1669,16 @@
         <v>17</v>
       </c>
       <c r="E28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" t="s">
         <v>106</v>
-      </c>
-      <c r="F28" t="s">
-        <v>107</v>
       </c>
       <c r="H28" s="13">
         <v>2497</v>
       </c>
       <c r="I28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
@@ -1695,16 +1695,16 @@
         <v>32</v>
       </c>
       <c r="E29" t="s">
+        <v>105</v>
+      </c>
+      <c r="F29" t="s">
         <v>106</v>
-      </c>
-      <c r="F29" t="s">
-        <v>107</v>
       </c>
       <c r="H29" s="13">
         <v>2497</v>
       </c>
       <c r="I29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
@@ -1721,16 +1721,16 @@
         <v>30</v>
       </c>
       <c r="E30" t="s">
+        <v>105</v>
+      </c>
+      <c r="F30" t="s">
         <v>106</v>
-      </c>
-      <c r="F30" t="s">
-        <v>107</v>
       </c>
       <c r="H30" s="13">
         <v>2497</v>
       </c>
       <c r="I30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
@@ -1747,16 +1747,16 @@
         <v>16</v>
       </c>
       <c r="E31" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" t="s">
         <v>106</v>
-      </c>
-      <c r="F31" t="s">
-        <v>107</v>
       </c>
       <c r="H31" s="13">
         <v>2497</v>
       </c>
       <c r="I31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
@@ -1773,16 +1773,16 @@
         <v>29</v>
       </c>
       <c r="E32" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" t="s">
         <v>106</v>
-      </c>
-      <c r="F32" t="s">
-        <v>107</v>
       </c>
       <c r="H32" s="13">
         <v>2497</v>
       </c>
       <c r="I32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -1799,16 +1799,16 @@
         <v>14</v>
       </c>
       <c r="E33" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" t="s">
         <v>106</v>
-      </c>
-      <c r="F33" t="s">
-        <v>107</v>
       </c>
       <c r="H33" s="13">
         <v>2497</v>
       </c>
       <c r="I33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
@@ -1825,16 +1825,16 @@
         <v>20</v>
       </c>
       <c r="E34" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" t="s">
         <v>106</v>
-      </c>
-      <c r="F34" t="s">
-        <v>107</v>
       </c>
       <c r="H34" s="13">
         <v>2497</v>
       </c>
       <c r="I34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1876,7 +1876,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>22</v>
@@ -1907,13 +1907,13 @@
         <v>29</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
@@ -1942,10 +1942,10 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="N7" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
@@ -1961,10 +1961,10 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="N8" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
@@ -1988,35 +1988,35 @@
     </row>
     <row r="10" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>39</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>36</v>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -2064,7 +2064,7 @@
         <v>39</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
@@ -2080,49 +2080,49 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="N13" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
@@ -2157,7 +2157,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="N16" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O16" s="4" t="s">
         <v>45</v>
@@ -2171,15 +2171,15 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>45</v>
@@ -2190,35 +2190,35 @@
     </row>
     <row r="18" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="10" t="s">
         <v>36</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="G18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="H18" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>48</v>
@@ -2243,7 +2243,7 @@
         <v>44</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
@@ -2291,7 +2291,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -2302,43 +2302,43 @@
         <v>42</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>36</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>41</v>
@@ -2357,50 +2357,50 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="N24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="O24" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="25" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="N25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="N26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N27" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F28" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O28" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O29" s="4" t="s">
         <v>40</v>
@@ -2408,7 +2408,7 @@
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N30" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O30" s="4" t="s">
         <v>42</v>
@@ -2416,17 +2416,17 @@
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N31" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="C32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.2">
@@ -2446,17 +2446,17 @@
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="3:3" x14ac:dyDescent="0.2">
@@ -2481,7 +2481,7 @@
     </row>
     <row r="44" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="3:3" x14ac:dyDescent="0.2">
@@ -2496,7 +2496,7 @@
     </row>
     <row r="47" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="3:3" x14ac:dyDescent="0.2">
@@ -2511,27 +2511,27 @@
     </row>
     <row r="50" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C52" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="3:3" x14ac:dyDescent="0.2">
@@ -2571,7 +2571,7 @@
     </row>
     <row r="62" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C62" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="3:3" x14ac:dyDescent="0.2">
@@ -2662,7 +2662,7 @@
     </row>
     <row r="7" spans="3:3" ht="105.75" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="3:3" ht="15" x14ac:dyDescent="0.2">
@@ -2752,7 +2752,7 @@
         <v>29</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>30</v>
@@ -2778,7 +2778,7 @@
     </row>
     <row r="6" spans="3:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>37</v>
@@ -2796,7 +2796,7 @@
         <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>41</v>
@@ -2805,7 +2805,7 @@
         <v>42</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="3:14" ht="15" x14ac:dyDescent="0.2">
@@ -2816,67 +2816,67 @@
         <v>37</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="3:14" ht="15" x14ac:dyDescent="0.2">
       <c r="E8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="3:14" x14ac:dyDescent="0.2">
       <c r="E9" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>37</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I14" s="3"/>
       <c r="K14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="3:14" x14ac:dyDescent="0.2">
@@ -2971,7 +2971,7 @@
         <v>39</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>34</v>
@@ -2989,10 +2989,10 @@
         <v>39</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U19" s="3" t="s">
         <v>40</v>
@@ -3007,10 +3007,10 @@
       </c>
       <c r="I20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>45</v>
@@ -3031,10 +3031,10 @@
         <v>42</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="2:21" ht="15" x14ac:dyDescent="0.2">
@@ -3042,38 +3042,38 @@
         <v>21</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="N21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>34</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:21" ht="15" x14ac:dyDescent="0.2">
@@ -3088,31 +3088,31 @@
         <v>40</v>
       </c>
       <c r="M22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="N22" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="O22" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T22" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="U22" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
@@ -3145,7 +3145,7 @@
         <v>44</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.2">
@@ -3168,17 +3168,17 @@
     </row>
     <row r="29" spans="2:21" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>36</v>
@@ -3186,17 +3186,17 @@
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>38</v>
@@ -3207,14 +3207,14 @@
         <v>33</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>39</v>
@@ -3225,17 +3225,17 @@
         <v>36</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I32" s="3"/>
       <c r="K32" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.2">
@@ -3243,32 +3243,32 @@
         <v>33</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I33" s="3"/>
       <c r="K33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>40</v>
@@ -3276,35 +3276,35 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I35" s="3"/>
       <c r="K35" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>45</v>
@@ -3315,14 +3315,14 @@
         <v>35</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>48</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="I38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>44</v>
@@ -3354,10 +3354,10 @@
         <v>44</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I40" s="3"/>
       <c r="M40" s="3" t="s">
@@ -3366,13 +3366,13 @@
     </row>
     <row r="41" spans="2:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I41" s="3"/>
       <c r="M41" s="3" t="s">
@@ -3384,14 +3384,14 @@
         <v>38</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.2">
@@ -3402,25 +3402,25 @@
         <v>36</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.2">
@@ -3428,13 +3428,13 @@
         <v>41</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.2">
@@ -3442,62 +3442,62 @@
         <v>47</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B49" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.2">
@@ -3523,14 +3523,14 @@
     </row>
     <row r="61" spans="2:13" ht="15" x14ac:dyDescent="0.2">
       <c r="E61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F61">
         <f>VLOOKUP(E61,$J$60:$K$103,2,FALSE)</f>
         <v>1005</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K61">
         <v>1000</v>
@@ -3541,14 +3541,14 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E62" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F62">
         <f t="shared" ref="F62:F96" si="0">VLOOKUP(E62,$J$60:$K$103,2,FALSE)</f>
         <v>1007</v>
       </c>
       <c r="J62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K62">
         <v>1001</v>
@@ -3620,7 +3620,7 @@
         <v>1016</v>
       </c>
       <c r="J66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K66">
         <v>1005</v>
@@ -3638,7 +3638,7 @@
         <v>1017</v>
       </c>
       <c r="J67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K67">
         <v>1006</v>
@@ -3649,14 +3649,14 @@
     </row>
     <row r="68" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F68">
         <f t="shared" si="0"/>
         <v>1022</v>
       </c>
       <c r="J68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K68">
         <v>1007</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="70" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E70" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F70">
         <f t="shared" si="0"/>
@@ -3746,7 +3746,7 @@
         <v>1008</v>
       </c>
       <c r="J73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K73">
         <v>1012</v>
@@ -3793,14 +3793,14 @@
     </row>
     <row r="76" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E76" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F76">
         <f t="shared" si="0"/>
         <v>1018</v>
       </c>
       <c r="J76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K76">
         <v>1015</v>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="77" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E77" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F77">
         <f t="shared" si="0"/>
@@ -3847,14 +3847,14 @@
     </row>
     <row r="79" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E79" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F79">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="J79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K79">
         <v>1018</v>
@@ -3865,14 +3865,14 @@
     </row>
     <row r="80" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E80" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F80">
         <f t="shared" si="0"/>
         <v>1001</v>
       </c>
       <c r="J80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K80">
         <v>1019</v>
@@ -3890,7 +3890,7 @@
         <v>1002</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K81">
         <v>1020</v>
@@ -3908,7 +3908,7 @@
         <v>1003</v>
       </c>
       <c r="J82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K82">
         <v>1021</v>
@@ -3919,14 +3919,14 @@
     </row>
     <row r="83" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F83">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="J83" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K83">
         <v>1022</v>
@@ -3937,7 +3937,7 @@
     </row>
     <row r="84" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E84" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F84">
         <f t="shared" si="0"/>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="85" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E85" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F85">
         <f t="shared" si="0"/>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="86" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E86" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F86">
         <f t="shared" si="0"/>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="87" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F87">
         <f t="shared" si="0"/>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="88" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E88" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F88">
         <f t="shared" si="0"/>
@@ -4027,7 +4027,7 @@
     </row>
     <row r="89" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E89" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F89">
         <f t="shared" si="0"/>
@@ -4063,14 +4063,14 @@
     </row>
     <row r="91" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E91" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F91">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K91">
         <v>1105</v>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="92" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E92" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F92">
         <f t="shared" si="0"/>
@@ -4099,7 +4099,7 @@
     </row>
     <row r="93" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E93" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F93">
         <f t="shared" si="0"/>
@@ -4117,7 +4117,7 @@
     </row>
     <row r="94" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E94" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F94">
         <f t="shared" si="0"/>
@@ -4135,7 +4135,7 @@
     </row>
     <row r="95" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E95" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F95">
         <f t="shared" si="0"/>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="96" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F96">
         <f t="shared" si="0"/>
@@ -4275,7 +4275,7 @@
         <v>41</v>
       </c>
       <c r="F115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="5:6" x14ac:dyDescent="0.2">
@@ -4283,7 +4283,7 @@
         <v>45</v>
       </c>
       <c r="F116" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="117" spans="5:6" x14ac:dyDescent="0.2">
@@ -4291,15 +4291,15 @@
         <v>42</v>
       </c>
       <c r="F117" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E118" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F118" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="5:6" x14ac:dyDescent="0.2">
@@ -4336,18 +4336,18 @@
     </row>
     <row r="123" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E123" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F123" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="124" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E124" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F124" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="125" spans="5:6" x14ac:dyDescent="0.2">
@@ -4363,7 +4363,7 @@
         <v>47</v>
       </c>
       <c r="F126" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="127" spans="5:6" x14ac:dyDescent="0.2">
@@ -4371,15 +4371,15 @@
         <v>39</v>
       </c>
       <c r="F127" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="128" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E128" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F128" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="129" spans="5:6" x14ac:dyDescent="0.2">
@@ -4387,7 +4387,7 @@
         <v>38</v>
       </c>
       <c r="F129" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="130" spans="5:6" x14ac:dyDescent="0.2">
@@ -4403,15 +4403,15 @@
         <v>33</v>
       </c>
       <c r="F131" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="132" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E132" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F132" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="133" spans="5:6" x14ac:dyDescent="0.2">
@@ -4424,10 +4424,10 @@
     </row>
     <row r="134" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E134" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F134" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="135" spans="5:6" x14ac:dyDescent="0.2">
@@ -4440,18 +4440,18 @@
     </row>
     <row r="136" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E136" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="137" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E137" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F137" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="138" spans="5:6" x14ac:dyDescent="0.2">
@@ -4459,7 +4459,7 @@
         <v>35</v>
       </c>
       <c r="F138" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="139" spans="5:6" x14ac:dyDescent="0.2">
@@ -4488,15 +4488,15 @@
     </row>
     <row r="142" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E142" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F142" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="143" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E143" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F143">
         <v>2497</v>
@@ -4504,18 +4504,18 @@
     </row>
     <row r="144" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E144" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F144" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="145" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E145" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F145" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="146" spans="5:6" x14ac:dyDescent="0.2">
@@ -4528,10 +4528,10 @@
     </row>
     <row r="147" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E147" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F147" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="148" spans="5:6" x14ac:dyDescent="0.2">
@@ -4539,7 +4539,7 @@
         <v>44</v>
       </c>
       <c r="F148" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="149" spans="5:6" x14ac:dyDescent="0.2">
@@ -4547,7 +4547,7 @@
         <v>36</v>
       </c>
       <c r="F149" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="150" spans="5:6" x14ac:dyDescent="0.2">
@@ -4555,7 +4555,7 @@
         <v>40</v>
       </c>
       <c r="F150" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="151" spans="5:6" x14ac:dyDescent="0.2">
@@ -4563,12 +4563,12 @@
         <v>43</v>
       </c>
       <c r="F151" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="152" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E152" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F152">
         <v>2497</v>

--- a/Datas/FishData.xlsx
+++ b/Datas/FishData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="FishData" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="149">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -565,6 +565,64 @@
       </rPr>
       <t>Angelfish, Arapaima, Arowana, Barbel Steed, Betta, Bitterling, Black Bass, Bluegill, Brook Trout, Crucian Carp, Dace, Dorado, Freshwater Eel, Freshwater Goby, Giant Catfish, Guppy, Herabuna, Large Bass, Loach, Mitten Crab, Neon Tetra, Nibble Fish, Pale Chub, Pike, Piranha, Pond Smelt, Rainbow Trout, Saddled Bichir, Snapping Turtle, Soft-Shelled Turtle (Green), Soft-Shelled Turtle (Brown), Soft-Shelled Turtle (Black), Sweetfish</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鲯鳅鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝蟹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红鲷鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斑马狮子鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条石鲷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河蟹.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河蟹</t>
+  </si>
+  <si>
+    <t>金线鱼</t>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙丁鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹荚鱼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -615,7 +673,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -634,6 +692,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -647,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -684,6 +748,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -967,7 +1039,8 @@
   <dimension ref="A2:I34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="10.375" customWidth="1"/>
+    <col min="3" max="3" width="10.375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
     <col min="5" max="5" width="15.375" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
     <col min="8" max="8" width="17.5" style="13" customWidth="1"/>
@@ -980,7 +1053,7 @@
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
@@ -1009,7 +1082,7 @@
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
@@ -1038,7 +1111,7 @@
       <c r="B4" s="5">
         <v>4000</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1053,7 +1126,7 @@
       <c r="H4" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="14" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1064,7 +1137,7 @@
       <c r="B5" s="5">
         <v>4006</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="15" t="s">
         <v>63</v>
       </c>
       <c r="D5" t="s">
@@ -1079,8 +1152,8 @@
       <c r="H5" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="I5" t="s">
-        <v>115</v>
+      <c r="I5" s="14" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -1090,11 +1163,11 @@
       <c r="B6" s="5">
         <v>4007</v>
       </c>
-      <c r="C6" t="s">
-        <v>49</v>
+      <c r="C6" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
         <v>105</v>
@@ -1105,8 +1178,8 @@
       <c r="H6" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="I6" t="s">
-        <v>115</v>
+      <c r="I6" s="14" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -1116,7 +1189,7 @@
       <c r="B7" s="5">
         <v>4009</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="15" t="s">
         <v>45</v>
       </c>
       <c r="D7" t="s">
@@ -1131,7 +1204,7 @@
       <c r="H7" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="14" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1142,7 +1215,7 @@
       <c r="B8" s="5">
         <v>4010</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="17" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -1157,7 +1230,7 @@
       <c r="H8" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="14" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1168,11 +1241,11 @@
       <c r="B9" s="5">
         <v>4011</v>
       </c>
-      <c r="C9" t="s">
-        <v>44</v>
+      <c r="C9" s="15" t="s">
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
         <v>105</v>
@@ -1183,7 +1256,7 @@
       <c r="H9" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="14" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1194,7 +1267,7 @@
       <c r="B10" s="5">
         <v>4013</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="15" t="s">
         <v>38</v>
       </c>
       <c r="D10" t="s">
@@ -1209,8 +1282,8 @@
       <c r="H10" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="I10" t="s">
-        <v>115</v>
+      <c r="I10" s="14">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -1220,7 +1293,7 @@
       <c r="B11" s="5">
         <v>4014</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="15" t="s">
         <v>43</v>
       </c>
       <c r="D11" t="s">
@@ -1235,8 +1308,8 @@
       <c r="H11" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="I11" t="s">
-        <v>115</v>
+      <c r="I11" s="14" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -1246,7 +1319,7 @@
       <c r="B12" s="5">
         <v>4015</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="15" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
@@ -1261,8 +1334,8 @@
       <c r="H12" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="I12" t="s">
-        <v>115</v>
+      <c r="I12" s="14">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -1272,7 +1345,7 @@
       <c r="B13" s="5">
         <v>4016</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="15" t="s">
         <v>41</v>
       </c>
       <c r="D13" t="s">
@@ -1287,8 +1360,8 @@
       <c r="H13" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="I13" t="s">
-        <v>115</v>
+      <c r="I13" s="14" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -1298,7 +1371,7 @@
       <c r="B14" s="5">
         <v>4017</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="15" t="s">
         <v>47</v>
       </c>
       <c r="D14" t="s">
@@ -1313,8 +1386,8 @@
       <c r="H14" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="I14" t="s">
-        <v>115</v>
+      <c r="I14" s="14">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -1324,7 +1397,7 @@
       <c r="B15" s="5">
         <v>4018</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="15" t="s">
         <v>58</v>
       </c>
       <c r="D15" t="s">
@@ -1339,8 +1412,8 @@
       <c r="H15" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="I15" t="s">
-        <v>115</v>
+      <c r="I15" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -1350,7 +1423,7 @@
       <c r="B16" s="5">
         <v>4020</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="17" t="s">
         <v>72</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -1365,8 +1438,8 @@
       <c r="H16" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="I16" t="s">
-        <v>115</v>
+      <c r="I16" s="14" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -1376,7 +1449,7 @@
       <c r="B17" s="5">
         <v>4021</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D17" t="s">
@@ -1391,8 +1464,8 @@
       <c r="H17" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="I17" t="s">
-        <v>115</v>
+      <c r="I17" s="14" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1402,7 +1475,7 @@
       <c r="B18" s="5">
         <v>4022</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="15" t="s">
         <v>57</v>
       </c>
       <c r="D18" t="s">
@@ -1417,8 +1490,8 @@
       <c r="H18" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="I18" t="s">
-        <v>115</v>
+      <c r="I18" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1428,7 +1501,7 @@
       <c r="B19" s="5">
         <v>4023</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D19" t="s">
@@ -1443,8 +1516,8 @@
       <c r="H19" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="I19" t="s">
-        <v>115</v>
+      <c r="I19" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1454,8 +1527,8 @@
       <c r="B20" s="5">
         <v>4024</v>
       </c>
-      <c r="C20" t="s">
-        <v>42</v>
+      <c r="C20" s="15" t="s">
+        <v>146</v>
       </c>
       <c r="D20" t="s">
         <v>42</v>
@@ -1469,8 +1542,8 @@
       <c r="H20" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="I20" t="s">
-        <v>115</v>
+      <c r="I20" s="14">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -1480,8 +1553,8 @@
       <c r="B21" s="5">
         <v>4100</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>24</v>
+      <c r="C21" s="17" t="s">
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>24</v>
@@ -1495,7 +1568,7 @@
       <c r="H21" s="13">
         <v>2497</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="14" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1506,8 +1579,8 @@
       <c r="B22" s="5">
         <v>4101</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>25</v>
+      <c r="C22" s="17" t="s">
+        <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -1522,7 +1595,7 @@
         <v>2497</v>
       </c>
       <c r="I22" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -1532,7 +1605,7 @@
       <c r="B23" s="5">
         <v>4103</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="17" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -1548,7 +1621,7 @@
         <v>2497</v>
       </c>
       <c r="I23" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
@@ -1558,7 +1631,7 @@
       <c r="B24" s="5">
         <v>4105</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="17" t="s">
         <v>125</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -1573,7 +1646,7 @@
       <c r="H24" s="13">
         <v>2497</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="14" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1584,7 +1657,7 @@
       <c r="B25" s="5">
         <v>4106</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="17" t="s">
         <v>26</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -1599,8 +1672,8 @@
       <c r="H25" s="13">
         <v>2497</v>
       </c>
-      <c r="I25" t="s">
-        <v>115</v>
+      <c r="I25" s="14">
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
@@ -1610,7 +1683,7 @@
       <c r="B26" s="5">
         <v>4109</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -1625,7 +1698,7 @@
       <c r="H26" s="13">
         <v>2497</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="14" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1636,7 +1709,7 @@
       <c r="B27" s="5">
         <v>4110</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="17" t="s">
         <v>73</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -1652,7 +1725,7 @@
         <v>2497</v>
       </c>
       <c r="I27" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
@@ -1662,8 +1735,8 @@
       <c r="B28" s="5">
         <v>4111</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>17</v>
+      <c r="C28" s="17" t="s">
+        <v>142</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>17</v>
@@ -1678,7 +1751,7 @@
         <v>2497</v>
       </c>
       <c r="I28" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
@@ -1688,8 +1761,8 @@
       <c r="B29" s="5">
         <v>4112</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>32</v>
+      <c r="C29" s="17" t="s">
+        <v>140</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>32</v>
@@ -1704,7 +1777,7 @@
         <v>2497</v>
       </c>
       <c r="I29" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
@@ -1714,8 +1787,8 @@
       <c r="B30" s="5">
         <v>4113</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>30</v>
+      <c r="C30" s="17" t="s">
+        <v>139</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>30</v>
@@ -1730,7 +1803,7 @@
         <v>2497</v>
       </c>
       <c r="I30" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
@@ -1740,8 +1813,8 @@
       <c r="B31" s="5">
         <v>4114</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>16</v>
+      <c r="C31" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>16</v>
@@ -1755,8 +1828,8 @@
       <c r="H31" s="13">
         <v>2497</v>
       </c>
-      <c r="I31" t="s">
-        <v>115</v>
+      <c r="I31">
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
@@ -1766,7 +1839,7 @@
       <c r="B32" s="5">
         <v>4115</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -1781,8 +1854,8 @@
       <c r="H32" s="13">
         <v>2497</v>
       </c>
-      <c r="I32" t="s">
-        <v>115</v>
+      <c r="I32" s="14">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -1792,7 +1865,7 @@
       <c r="B33" s="5">
         <v>4116</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -1807,8 +1880,8 @@
       <c r="H33" s="13">
         <v>2497</v>
       </c>
-      <c r="I33" t="s">
-        <v>115</v>
+      <c r="I33">
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
@@ -1818,8 +1891,8 @@
       <c r="B34" s="5">
         <v>4117</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>20</v>
+      <c r="C34" s="17" t="s">
+        <v>141</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>20</v>
@@ -1833,8 +1906,8 @@
       <c r="H34" s="13">
         <v>2497</v>
       </c>
-      <c r="I34" t="s">
-        <v>115</v>
+      <c r="I34">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2423,163 +2496,442 @@
       <c r="C32" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F32" s="5">
+        <v>4000</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F33" s="5">
+        <v>4006</v>
+      </c>
+      <c r="G33" t="s">
+        <v>63</v>
+      </c>
+      <c r="J33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F34" s="5">
+        <v>4007</v>
+      </c>
+      <c r="G34" t="s">
+        <v>49</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C35" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F35" s="5">
+        <v>4009</v>
+      </c>
+      <c r="G35" t="s">
+        <v>45</v>
+      </c>
+      <c r="J35" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F36" s="5">
+        <v>4010</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F37" s="5">
+        <v>4011</v>
+      </c>
+      <c r="G37" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F38" s="5">
+        <v>4013</v>
+      </c>
+      <c r="G38" t="s">
+        <v>38</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C39" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F39" s="5">
+        <v>4014</v>
+      </c>
+      <c r="G39" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C40" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F40" s="5">
+        <v>4015</v>
+      </c>
+      <c r="G40" t="s">
+        <v>64</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C41" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F41" s="5">
+        <v>4016</v>
+      </c>
+      <c r="G41" t="s">
+        <v>41</v>
+      </c>
+      <c r="J41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C42" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F42" s="5">
+        <v>4017</v>
+      </c>
+      <c r="G42" t="s">
+        <v>47</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F43" s="5">
+        <v>4018</v>
+      </c>
+      <c r="G43" t="s">
+        <v>58</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F44" s="5">
+        <v>4020</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J44" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F45" s="5">
+        <v>4021</v>
+      </c>
+      <c r="G45" t="s">
+        <v>55</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F46" s="5">
+        <v>4022</v>
+      </c>
+      <c r="G46" t="s">
+        <v>57</v>
+      </c>
+      <c r="J46" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F47" s="5">
+        <v>4023</v>
+      </c>
+      <c r="G47" t="s">
+        <v>40</v>
+      </c>
+      <c r="J47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C48" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F48" s="5">
+        <v>4024</v>
+      </c>
+      <c r="G48" t="s">
+        <v>42</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C49" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F49" s="5">
+        <v>4100</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C50" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F50" s="5">
+        <v>4101</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C51" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F51" s="5">
+        <v>4103</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C52" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F52" s="5">
+        <v>4105</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C53" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F53" s="5">
+        <v>4106</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C54" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F54" s="5">
+        <v>4109</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C55" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F55" s="5">
+        <v>4110</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C56" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F56" s="5">
+        <v>4111</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C57" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F57" s="5">
+        <v>4112</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C58" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F58" s="5">
+        <v>4113</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C59" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F59" s="5">
+        <v>4114</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C60" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F60" s="5">
+        <v>4115</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="C61" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F61" s="5">
+        <v>4116</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="C62" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="F62" s="5">
+        <v>4117</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C63" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:10" x14ac:dyDescent="0.2">
       <c r="C64" s="3" t="s">
         <v>27</v>
       </c>
